--- a/docs/files/exports/combined-combined-pricing-quick-guide.xlsx
+++ b/docs/files/exports/combined-combined-pricing-quick-guide.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Combined Web + App Pricing Quick Reference Guide</t>
+          <t>Pricing Quick Reference Guide</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2,788 words</t>
+          <t>2,756 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Combined Web + App Pricing Quick Reference Guide Quick-reference pricing guide for full-stack engagements covering both website and mobile application pricing tiers at a glance. Scope: This document covers both Web / Web...</t>
+          <t>Pricing Quick Reference Guide Fast-reference pricing guide for full-stack client engagements covering pricing formulas, cost ranges, key drivers, technology recommendations, and common pitfalls for both Website and Mobil...</t>
         </is>
       </c>
     </row>
